--- a/data/trans_camb/P6903-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/P6903-Habitat-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-14,54; 13,52</t>
+          <t>-15,87; 13,94</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-8,05; 25,56</t>
+          <t>-8,14; 27,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-10,44; 22,54</t>
+          <t>-12,95; 18,77</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-22,76; 26,71</t>
+          <t>-22,08; 24,49</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-23,82; 23,46</t>
+          <t>-23,25; 27,05</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-16,09; 22,14</t>
+          <t>-17,27; 20,77</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-12,9; 11,24</t>
+          <t>-13,17; 11,41</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-6,74; 20,54</t>
+          <t>-6,78; 19,67</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-7,41; 17,42</t>
+          <t>-6,27; 17,28</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-45,97; 72,49</t>
+          <t>-46,0; 76,81</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-25,36; 139,57</t>
+          <t>-24,52; 139,89</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-34,0; 131,93</t>
+          <t>-41,2; 93,88</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-50,04; 110,17</t>
+          <t>-46,53; 111,44</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-53,34; 94,38</t>
+          <t>-49,26; 120,63</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-34,0; 97,42</t>
+          <t>-35,98; 92,55</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-37,66; 46,93</t>
+          <t>-37,8; 49,74</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-20,05; 92,92</t>
+          <t>-21,56; 83,06</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-21,69; 75,16</t>
+          <t>-17,61; 82,58</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-21,44; 2,61</t>
+          <t>-22,11; 2,14</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-11,97; 15,48</t>
+          <t>-12,96; 14,34</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-8,1; 18,19</t>
+          <t>-7,65; 18,51</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-4,44; 30,83</t>
+          <t>-4,7; 29,4</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2,67; 39,06</t>
+          <t>3,91; 38,83</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,45; 31,56</t>
+          <t>1,51; 30,43</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-11,71; 7,84</t>
+          <t>-12,33; 7,81</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-3,07; 17,9</t>
+          <t>-3,89; 18,97</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-1,19; 18,29</t>
+          <t>-1,71; 17,36</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-57,77; 8,71</t>
+          <t>-58,02; 9,77</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-31,62; 54,03</t>
+          <t>-35,0; 51,55</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-22,09; 64,98</t>
+          <t>-21,96; 66,22</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-16,39; 225,65</t>
+          <t>-16,73; 206,57</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>6,44; 269,17</t>
+          <t>9,75; 267,74</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>5,71; 245,39</t>
+          <t>0,15; 212,39</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-34,61; 30,3</t>
+          <t>-35,99; 32,0</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-9,02; 69,63</t>
+          <t>-11,8; 71,64</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-3,37; 72,67</t>
+          <t>-5,24; 67,3</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-10,98; 16,81</t>
+          <t>-10,63; 17,45</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,4; 28,27</t>
+          <t>2,88; 30,01</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,37; 30,58</t>
+          <t>-2,75; 29,94</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-22,69; 13,41</t>
+          <t>-22,47; 13,07</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-5,42; 29,85</t>
+          <t>-5,39; 29,65</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-30,73; 17,26</t>
+          <t>-33,07; 16,1</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-9,82; 11,4</t>
+          <t>-10,04; 11,93</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>4,14; 25,23</t>
+          <t>4,52; 26,17</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-16,91; 18,07</t>
+          <t>-15,07; 18,48</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-35,14; 87,41</t>
+          <t>-35,33; 89,09</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>7,82; 151,18</t>
+          <t>7,32; 158,09</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-7,24; 154,76</t>
+          <t>-9,52; 154,22</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-55,42; 64,26</t>
+          <t>-54,94; 59,04</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-12,63; 138,87</t>
+          <t>-12,84; 131,47</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-69,93; 64,69</t>
+          <t>-73,38; 55,47</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-30,72; 48,31</t>
+          <t>-31,2; 53,98</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>12,88; 112,11</t>
+          <t>12,47; 122,38</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-46,7; 74,08</t>
+          <t>-45,27; 75,57</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-32,01; -6,51</t>
+          <t>-30,57; -6,84</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-7,92; 19,29</t>
+          <t>-7,35; 18,96</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-19,64; 6,7</t>
+          <t>-19,02; 5,88</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-10,9; 21,63</t>
+          <t>-10,8; 19,83</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-11,2; 22,26</t>
+          <t>-11,74; 18,35</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,29; 29,03</t>
+          <t>2,01; 30,42</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-17,95; 1,72</t>
+          <t>-18,15; 1,68</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-4,3; 14,93</t>
+          <t>-5,8; 14,8</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-6,23; 12,55</t>
+          <t>-5,71; 13,1</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-72,67; -19,31</t>
+          <t>-70,09; -18,22</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-18,8; 58,98</t>
+          <t>-17,04; 56,36</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-45,96; 22,39</t>
+          <t>-45,2; 17,94</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-28,6; 81,26</t>
+          <t>-29,61; 74,12</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-29,07; 86,69</t>
+          <t>-29,71; 69,71</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,9; 117,64</t>
+          <t>5,25; 120,24</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-45,71; 5,51</t>
+          <t>-45,8; 5,99</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-11,55; 46,75</t>
+          <t>-15,39; 47,74</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-15,09; 39,58</t>
+          <t>-14,22; 41,74</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-14,13; -1,34</t>
+          <t>-13,82; -0,63</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,2; 14,16</t>
+          <t>0,34; 14,16</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-4,73; 10,38</t>
+          <t>-4,45; 9,63</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-5,4; 12,8</t>
+          <t>-5,52; 13,35</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>2,1; 19,88</t>
+          <t>1,41; 20,43</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-4,25; 17,25</t>
+          <t>-3,79; 16,95</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-8,19; 1,88</t>
+          <t>-8,41; 2,44</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>3,17; 14,26</t>
+          <t>3,3; 14,52</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-1,51; 10,88</t>
+          <t>-2,01; 10,84</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-40,79; -4,91</t>
+          <t>-40,49; -2,09</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>0,38; 50,01</t>
+          <t>1,02; 49,35</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-14,09; 35,78</t>
+          <t>-13,54; 33,1</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-15,47; 48,02</t>
+          <t>-15,07; 52,06</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>6,26; 78,9</t>
+          <t>4,13; 78,2</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-10,7; 64,66</t>
+          <t>-9,18; 62,47</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-24,12; 6,57</t>
+          <t>-25,2; 8,32</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>9,51; 50,71</t>
+          <t>9,69; 49,85</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-4,53; 36,91</t>
+          <t>-5,73; 37,27</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P6903-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/P6903-Habitat-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3,78</t>
+          <t>5,38</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,43</t>
+          <t>4,53</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>5,02</t>
+          <t>6,48</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-15,87; 13,94</t>
+          <t>-14,99; 13,96</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-8,14; 27,0</t>
+          <t>-7,41; 26,63</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-12,95; 18,77</t>
+          <t>-10,57; 23,62</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-22,08; 24,49</t>
+          <t>-22,43; 24,55</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-23,25; 27,05</t>
+          <t>-23,9; 25,05</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-17,27; 20,77</t>
+          <t>-16,07; 23,35</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-13,17; 11,41</t>
+          <t>-11,91; 12,95</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-6,78; 19,67</t>
+          <t>-8,46; 19,75</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-6,27; 17,28</t>
+          <t>-5,58; 21,2</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>14,32%</t>
+          <t>20,37%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>9,54%</t>
+          <t>12,6%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>17,21%</t>
+          <t>22,22%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-46,0; 76,81</t>
+          <t>-45,43; 77,79</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-24,52; 139,89</t>
+          <t>-24,29; 145,39</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-41,2; 93,88</t>
+          <t>-34,16; 122,68</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-46,53; 111,44</t>
+          <t>-51,89; 114,02</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-49,26; 120,63</t>
+          <t>-51,22; 106,12</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-35,98; 92,55</t>
+          <t>-33,16; 108,16</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-37,8; 49,74</t>
+          <t>-34,4; 61,05</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-21,56; 83,06</t>
+          <t>-23,58; 85,95</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-17,61; 82,58</t>
+          <t>-14,58; 104,65</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>4,44</t>
+          <t>6,85</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>17,58</t>
+          <t>17,71</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>8,53</t>
+          <t>9,85</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-22,11; 2,14</t>
+          <t>-21,73; 3,56</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-12,96; 14,34</t>
+          <t>-11,41; 14,71</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-7,65; 18,51</t>
+          <t>-5,86; 20,04</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-4,7; 29,4</t>
+          <t>-5,3; 30,14</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3,91; 38,83</t>
+          <t>5,71; 40,03</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,51; 30,43</t>
+          <t>2,09; 30,26</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-12,33; 7,81</t>
+          <t>-12,65; 6,96</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-3,89; 18,97</t>
+          <t>-2,58; 18,28</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-1,71; 17,36</t>
+          <t>1,17; 19,52</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>13,41%</t>
+          <t>20,67%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>76,79%</t>
+          <t>77,39%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>28,05%</t>
+          <t>32,4%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-58,02; 9,77</t>
+          <t>-57,41; 14,76</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-35,0; 51,55</t>
+          <t>-31,2; 55,05</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-21,96; 66,22</t>
+          <t>-15,73; 75,84</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-16,73; 206,57</t>
+          <t>-19,5; 205,89</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>9,75; 267,74</t>
+          <t>13,5; 283,23</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,15; 212,39</t>
+          <t>2,95; 215,76</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-35,99; 32,0</t>
+          <t>-36,75; 25,38</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-11,8; 71,64</t>
+          <t>-7,96; 72,59</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-5,24; 67,3</t>
+          <t>2,12; 77,97</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>13,7</t>
+          <t>12,42</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-4,5</t>
+          <t>10,72</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>4,55</t>
+          <t>13,1</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-10,63; 17,45</t>
+          <t>-10,6; 16,3</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,88; 30,01</t>
+          <t>1,91; 27,97</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-2,75; 29,94</t>
+          <t>-4,09; 29,04</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-22,47; 13,07</t>
+          <t>-21,55; 13,31</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-5,39; 29,65</t>
+          <t>-5,27; 29,79</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-33,07; 16,1</t>
+          <t>-8,01; 27,63</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-10,04; 11,93</t>
+          <t>-10,79; 10,94</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>4,52; 26,17</t>
+          <t>3,89; 25,57</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-15,07; 18,48</t>
+          <t>2,17; 24,33</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>54,13%</t>
+          <t>49,05%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-13,79%</t>
+          <t>32,88%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>16,54%</t>
+          <t>47,66%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-35,33; 89,09</t>
+          <t>-35,55; 83,53</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>7,32; 158,09</t>
+          <t>5,34; 150,94</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-9,52; 154,22</t>
+          <t>-13,83; 148,51</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-54,94; 59,04</t>
+          <t>-53,01; 60,8</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-12,84; 131,47</t>
+          <t>-11,7; 140,31</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-73,38; 55,47</t>
+          <t>-18,38; 128,25</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-31,2; 53,98</t>
+          <t>-33,51; 49,3</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>12,47; 122,38</t>
+          <t>11,42; 119,0</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-45,27; 75,57</t>
+          <t>7,27; 115,72</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-7,3</t>
+          <t>-4,89</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>15,31</t>
+          <t>12,89</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>3,55</t>
+          <t>3,4</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-30,57; -6,84</t>
+          <t>-31,1; -6,76</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-7,35; 18,96</t>
+          <t>-6,77; 19,58</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-19,02; 5,88</t>
+          <t>-17,97; 7,58</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-10,8; 19,83</t>
+          <t>-12,38; 20,48</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-11,74; 18,35</t>
+          <t>-13,88; 19,69</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,01; 30,42</t>
+          <t>0,1; 24,93</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-18,15; 1,68</t>
+          <t>-18,51; 1,05</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-5,8; 14,8</t>
+          <t>-6,15; 14,76</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-5,71; 13,1</t>
+          <t>-5,63; 11,68</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>-19,2%</t>
+          <t>-12,87%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>46,89%</t>
+          <t>39,48%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>9,88%</t>
+          <t>9,46%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-70,09; -18,22</t>
+          <t>-71,48; -17,1</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-17,04; 56,36</t>
+          <t>-17,68; 59,4</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-45,2; 17,94</t>
+          <t>-41,85; 23,52</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-29,61; 74,12</t>
+          <t>-30,59; 77,15</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-29,71; 69,71</t>
+          <t>-33,86; 74,09</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>5,25; 120,24</t>
+          <t>0,44; 101,38</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-45,8; 5,99</t>
+          <t>-47,53; 3,02</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-15,39; 47,74</t>
+          <t>-14,56; 45,77</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-14,22; 41,74</t>
+          <t>-13,76; 37,16</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2,6</t>
+          <t>4,44</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>8,32</t>
+          <t>11,88</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>5,37</t>
+          <t>7,84</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-13,82; -0,63</t>
+          <t>-14,03; -1,01</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,34; 14,16</t>
+          <t>-0,54; 14,48</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-4,45; 9,63</t>
+          <t>-2,31; 11,95</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-5,52; 13,35</t>
+          <t>-5,18; 13,04</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>1,41; 20,43</t>
+          <t>2,29; 20,53</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-3,79; 16,95</t>
+          <t>3,75; 19,09</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-8,41; 2,44</t>
+          <t>-8,02; 2,76</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>3,3; 14,52</t>
+          <t>2,87; 14,49</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-2,01; 10,84</t>
+          <t>2,59; 12,66</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>14,06%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>27,02%</t>
+          <t>38,61%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>17,13%</t>
+          <t>25,03%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-40,49; -2,09</t>
+          <t>-41,26; -4,26</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>1,02; 49,35</t>
+          <t>-0,78; 51,56</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-13,54; 33,1</t>
+          <t>-7,2; 43,04</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-15,07; 52,06</t>
+          <t>-14,61; 51,28</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>4,13; 78,2</t>
+          <t>5,88; 78,05</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-9,18; 62,47</t>
+          <t>10,53; 72,19</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-25,2; 8,32</t>
+          <t>-24,26; 10,46</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>9,69; 49,85</t>
+          <t>7,59; 49,2</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-5,73; 37,27</t>
+          <t>7,64; 44,38</t>
         </is>
       </c>
     </row>
